--- a/tests/fixtures/banks/synthetic/axis-retail-synthetic.xlsx
+++ b/tests/fixtures/banks/synthetic/axis-retail-synthetic.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:F29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -658,18 +658,15 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>NEFT CR-SYNTHETIC TRADERS-INVOICE</v>
+        <v>NEFT CR-SYNTHETIC TRADERS-INVOICE-SYNTN26296000032</v>
       </c>
       <c r="D20" t="str">
-        <v>SYNTN26296000032</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>1,40,000.00</v>
       </c>
       <c r="F20" t="str">
-        <v>1,40,000.00</v>
-      </c>
-      <c r="G20" t="str">
         <v>8,31,850.00</v>
       </c>
     </row>
@@ -761,18 +758,15 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>NEFT CR-SYNTHETIC ENTERPRISE-PROJECT ADVANCE</v>
+        <v>NEFT CR-SYNTHETIC ENTERPRISE-PROJECT ADVANCE-SYNTN26296000033</v>
       </c>
       <c r="D25" t="str">
-        <v>SYNTN26296000033</v>
+        <v/>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>95,000.00</v>
       </c>
       <c r="F25" t="str">
-        <v>95,000.00</v>
-      </c>
-      <c r="G25" t="str">
         <v>6,76,650.00</v>
       </c>
     </row>
@@ -816,7 +810,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
   </ignoredErrors>
 </worksheet>
 </file>